--- a/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 15,63</t>
+          <t>-13,89; 16,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 16,96</t>
+          <t>-16,68; 15,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 35,02</t>
+          <t>-4,43; 33,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,14; -5,11</t>
+          <t>-34,13; -4,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -8,04</t>
+          <t>-40,37; -9,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 20,94</t>
+          <t>-9,32; 21,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 2,73</t>
+          <t>-20,52; 1,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,0; -1,39</t>
+          <t>-23,73; -0,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 23,16</t>
+          <t>-1,39; 23,07</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 41,37</t>
+          <t>-26,77; 42,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 43,82</t>
+          <t>-30,75; 42,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 90,57</t>
+          <t>-7,76; 84,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,97; -8,83</t>
+          <t>-49,47; -8,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,86; -15,06</t>
+          <t>-57,81; -17,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 39,36</t>
+          <t>-12,66; 40,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 5,94</t>
+          <t>-35,57; 2,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -2,46</t>
+          <t>-41,39; -0,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 47,16</t>
+          <t>-2,31; 47,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 7,72</t>
+          <t>-4,36; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,56</t>
+          <t>-5,47; 5,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,77; 53,47</t>
+          <t>41,76; 53,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 5,78</t>
+          <t>-5,0; 6,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 4,42</t>
+          <t>-7,18; 4,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,13; 46,47</t>
+          <t>32,85; 46,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,94</t>
+          <t>-3,3; 5,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 3,57</t>
+          <t>-4,9; 3,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,61; 47,96</t>
+          <t>39,04; 48,0</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 26,74</t>
+          <t>-11,99; 27,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 18,48</t>
+          <t>-15,62; 18,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115,71; 186,48</t>
+          <t>116,12; 183,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 17,01</t>
+          <t>-13,7; 18,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 14,1</t>
+          <t>-18,62; 12,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,61; 146,21</t>
+          <t>86,76; 145,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 15,63</t>
+          <t>-9,14; 16,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 11,54</t>
+          <t>-13,76; 9,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109,38; 153,51</t>
+          <t>108,69; 154,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 14,46</t>
+          <t>-4,5; 14,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 14,8</t>
+          <t>-2,49; 15,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,5; 56,83</t>
+          <t>39,84; 57,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 7,38</t>
+          <t>-11,1; 7,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 7,63</t>
+          <t>-11,26; 7,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,52; 53,74</t>
+          <t>35,87; 53,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 7,87</t>
+          <t>-5,46; 8,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 8,74</t>
+          <t>-4,13; 9,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,54; 52,52</t>
+          <t>39,46; 52,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 56,43</t>
+          <t>-14,93; 59,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 60,5</t>
+          <t>-7,78; 63,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114,96; 243,07</t>
+          <t>118,1; 246,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 27,69</t>
+          <t>-30,54; 27,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 28,58</t>
+          <t>-29,72; 27,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91,17; 202,69</t>
+          <t>90,88; 203,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 28,68</t>
+          <t>-16,2; 30,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 31,57</t>
+          <t>-12,35; 33,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115,68; 197,29</t>
+          <t>112,28; 195,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,52</t>
+          <t>-2,38; 7,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,68</t>
+          <t>-3,69; 5,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,2; 50,05</t>
+          <t>40,08; 49,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,18</t>
+          <t>-7,06; 2,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,42</t>
+          <t>-9,02; 0,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,66</t>
+          <t>33,1; 42,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,49</t>
+          <t>-3,6; 3,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,03</t>
+          <t>-5,18; 1,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,89; 44,88</t>
+          <t>37,87; 44,6</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 24,59</t>
+          <t>-7,02; 24,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 18,32</t>
+          <t>-10,68; 19,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109,58; 165,14</t>
+          <t>109,97; 164,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 9,37</t>
+          <t>-17,82; 6,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 1,23</t>
+          <t>-22,12; 1,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,5; 122,86</t>
+          <t>83,62; 123,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 10,57</t>
+          <t>-9,66; 10,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 6,1</t>
+          <t>-14,18; 4,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103,7; 134,49</t>
+          <t>101,82; 135,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 16,66</t>
+          <t>-14,11; 16,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 15,96</t>
+          <t>-15,29; 17,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 33,11</t>
+          <t>-7,04; 34,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,13; -4,6</t>
+          <t>-34,16; -3,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,37; -9,6</t>
+          <t>-39,6; -9,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 21,16</t>
+          <t>-9,43; 20,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 1,24</t>
+          <t>-19,54; 1,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,73; -0,36</t>
+          <t>-23,76; -0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 23,07</t>
+          <t>-2,06; 23,39</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 42,74</t>
+          <t>-26,85; 43,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 42,54</t>
+          <t>-29,85; 43,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 84,21</t>
+          <t>-12,53; 88,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,47; -8,49</t>
+          <t>-49,92; -6,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,81; -17,25</t>
+          <t>-58,29; -17,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 40,64</t>
+          <t>-13,14; 37,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 2,38</t>
+          <t>-32,86; 4,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,39; -0,62</t>
+          <t>-39,96; -0,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 47,14</t>
+          <t>-2,98; 49,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 8,07</t>
+          <t>-4,97; 7,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 5,29</t>
+          <t>-6,09; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,76; 53,11</t>
+          <t>42,36; 53,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,14</t>
+          <t>-5,42; 5,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 4,13</t>
+          <t>-7,25; 4,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,85; 46,05</t>
+          <t>33,45; 46,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 5,16</t>
+          <t>-3,51; 5,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 3,1</t>
+          <t>-4,95; 3,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,04; 48,0</t>
+          <t>38,83; 47,71</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 27,96</t>
+          <t>-13,9; 26,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 18,16</t>
+          <t>-17,34; 20,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116,12; 183,37</t>
+          <t>117,61; 187,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 18,86</t>
+          <t>-14,12; 17,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 12,69</t>
+          <t>-19,05; 12,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,76; 145,32</t>
+          <t>86,64; 144,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 16,18</t>
+          <t>-9,99; 16,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 9,73</t>
+          <t>-13,74; 10,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>108,69; 154,08</t>
+          <t>107,53; 153,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 14,69</t>
+          <t>-5,36; 14,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 15,53</t>
+          <t>-3,58; 14,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,84; 57,41</t>
+          <t>39,53; 55,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 7,5</t>
+          <t>-11,65; 7,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 7,41</t>
+          <t>-11,67; 8,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,87; 53,98</t>
+          <t>35,7; 54,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 8,25</t>
+          <t>-5,58; 7,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 9,03</t>
+          <t>-4,07; 8,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,46; 52,31</t>
+          <t>40,55; 52,5</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 59,81</t>
+          <t>-16,52; 58,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 63,22</t>
+          <t>-10,18; 58,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118,1; 246,63</t>
+          <t>114,37; 237,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 27,99</t>
+          <t>-31,64; 26,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 27,01</t>
+          <t>-30,85; 28,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>90,88; 203,26</t>
+          <t>93,93; 204,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 30,22</t>
+          <t>-16,15; 28,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 33,45</t>
+          <t>-12,26; 32,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112,28; 195,42</t>
+          <t>116,51; 197,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,34</t>
+          <t>-1,92; 7,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,89</t>
+          <t>-3,58; 6,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,08; 49,71</t>
+          <t>39,78; 49,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,23</t>
+          <t>-6,68; 2,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 0,32</t>
+          <t>-8,87; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,76</t>
+          <t>33,02; 42,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,72</t>
+          <t>-3,03; 3,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,55</t>
+          <t>-4,56; 1,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,87; 44,6</t>
+          <t>37,9; 44,75</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 24,17</t>
+          <t>-5,61; 25,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 19,58</t>
+          <t>-10,0; 19,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109,97; 164,52</t>
+          <t>109,99; 162,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 6,14</t>
+          <t>-17,07; 8,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 1,17</t>
+          <t>-22,54; 1,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,62; 123,77</t>
+          <t>83,66; 124,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 10,98</t>
+          <t>-8,28; 10,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 4,52</t>
+          <t>-12,24; 5,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>101,82; 135,04</t>
+          <t>102,83; 136,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-19,59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-24,91</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,57</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-19,59</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-24,91</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>14,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 16,23</t>
+          <t>-35,14; -5,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 17,15</t>
+          <t>-40,02; -8,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 34,45</t>
+          <t>-9,65; 21,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,16; -3,75</t>
+          <t>-14,35; 15,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,6; -9,35</t>
+          <t>-16,7; 16,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 20,2</t>
+          <t>5,46; 36,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 1,42</t>
+          <t>-20,36; 2,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,76; -0,45</t>
+          <t>-24,0; -1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 23,39</t>
+          <t>2,27; 24,46</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-31,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-40,07%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>37,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-31,51%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-40,07%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 43,21</t>
+          <t>-50,97; -8,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 43,53</t>
+          <t>-57,86; -15,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 88,97</t>
+          <t>-13,67; 40,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,92; -6,65</t>
+          <t>-27,3; 41,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,29; -17,67</t>
+          <t>-32,78; 43,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 37,76</t>
+          <t>10,11; 99,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 4,22</t>
+          <t>-35,23; 5,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,96; -0,14</t>
+          <t>-40,79; -2,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 49,96</t>
+          <t>4,03; 51,01</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,67</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42,05</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,41</t>
+          <t>46,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43,76</t>
+          <t>43,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 7,68</t>
+          <t>-5,92; 5,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 5,9</t>
+          <t>-6,87; 4,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,36; 53,91</t>
+          <t>35,64; 47,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 5,92</t>
+          <t>-4,71; 7,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 4,06</t>
+          <t>-6,42; 5,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,45; 46,27</t>
+          <t>40,69; 51,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,08</t>
+          <t>-3,12; 4,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,34</t>
+          <t>-4,6; 3,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,83; 47,71</t>
+          <t>40,21; 48,02</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-4,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>118,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>147,17%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,74%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>114,27%</t>
+          <t>142,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>128,96%</t>
+          <t>129,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 26,3</t>
+          <t>-15,39; 17,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 20,52</t>
+          <t>-18,0; 14,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117,61; 187,11</t>
+          <t>93,93; 153,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 17,81</t>
+          <t>-13,55; 26,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 12,77</t>
+          <t>-18,21; 18,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,64; 144,13</t>
+          <t>113,44; 182,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 16,12</t>
+          <t>-8,69; 15,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 10,34</t>
+          <t>-12,61; 11,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>107,53; 153,78</t>
+          <t>111,34; 154,49</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,08</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45,69</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>6,02</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>48,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,08</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,21</t>
+          <t>48,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46,78</t>
+          <t>47,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 14,18</t>
+          <t>-10,66; 7,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 14,38</t>
+          <t>-10,47; 7,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,53; 55,51</t>
+          <t>36,13; 54,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 7,34</t>
+          <t>-3,83; 14,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 8,05</t>
+          <t>-3,3; 14,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,7; 54,25</t>
+          <t>40,02; 57,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 7,74</t>
+          <t>-5,14; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 8,83</t>
+          <t>-4,3; 8,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,55; 52,5</t>
+          <t>41,02; 52,93</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-6,38%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-4,98%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140,31%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>17,26%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>20,78%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>166,07%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-6,38%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-4,98%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>138,83%</t>
+          <t>167,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>152,51%</t>
+          <t>154,07%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 58,39</t>
+          <t>-28,47; 27,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 58,58</t>
+          <t>-28,48; 28,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114,37; 237,7</t>
+          <t>93,46; 204,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 26,22</t>
+          <t>-11,87; 56,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 28,85</t>
+          <t>-10,29; 60,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,93; 204,48</t>
+          <t>115,17; 245,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 28,98</t>
+          <t>-15,27; 28,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 32,82</t>
+          <t>-13,03; 31,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116,51; 197,89</t>
+          <t>117,61; 199,26</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,98</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39,6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44,92</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,98</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,34</t>
+          <t>44,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41,5</t>
+          <t>42,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,84</t>
+          <t>-6,71; 3,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 6,17</t>
+          <t>-8,87; 0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,78; 49,46</t>
+          <t>34,21; 43,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,96</t>
+          <t>-2,33; 7,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,61</t>
+          <t>-3,79; 5,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,02; 42,94</t>
+          <t>39,8; 49,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,71</t>
+          <t>-3,2; 3,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,92</t>
+          <t>-4,87; 2,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,9; 44,75</t>
+          <t>38,76; 45,25</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-5,83%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-10,66%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>106,14%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>7,72%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>136,5%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-5,83%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-10,66%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>102,76%</t>
+          <t>135,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>118,03%</t>
+          <t>119,48%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 25,77</t>
+          <t>-16,67; 9,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 19,76</t>
+          <t>-22,15; 1,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109,99; 162,77</t>
+          <t>84,68; 126,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 8,48</t>
+          <t>-6,75; 24,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 1,39</t>
+          <t>-10,76; 18,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,66; 124,13</t>
+          <t>109,89; 162,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 10,99</t>
+          <t>-8,62; 10,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 5,8</t>
+          <t>-13,37; 6,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>102,83; 136,52</t>
+          <t>105,28; 135,31</t>
         </is>
       </c>
     </row>
